--- a/ข้อมูล.xlsx
+++ b/ข้อมูล.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AFE9B4E-3573-4DC9-B022-3D7E5A25B4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3333CEA6-B866-440C-9639-AB83D3DC1903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{C89A9157-B32C-4594-9946-2ABBE017E0A7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C89A9157-B32C-4594-9946-2ABBE017E0A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>นายทองปิ่น จันทร์แปลง</t>
   </si>
@@ -48,9 +48,6 @@
     <t>นางวิภาดา จันทร์แปลง</t>
   </si>
   <si>
-    <t>ลูกจ้างรายวัน</t>
-  </si>
-  <si>
     <t>นายชาตรี เถาพุทธา</t>
   </si>
   <si>
@@ -91,6 +88,12 @@
   </si>
   <si>
     <t>รหัสบัญชี</t>
+  </si>
+  <si>
+    <t>ลจ.บริการฯ ตช. ทำหน้าที่เสมียน</t>
+  </si>
+  <si>
+    <t>ลจ.บริการฯ ตช. ทำหน้าที่คุมประประแจ</t>
   </si>
 </sst>
 </file>
@@ -474,7 +477,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="12.109375" bestFit="1" customWidth="1"/>
@@ -484,31 +487,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="19.8" x14ac:dyDescent="0.5">
@@ -519,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>1204536</v>
@@ -548,7 +551,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>2052576</v>
@@ -577,7 +580,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>2052564</v>
@@ -606,7 +609,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D5">
         <v>1574008</v>
@@ -632,10 +635,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>1535076</v>
@@ -661,10 +664,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D7">
         <v>1536733</v>
